--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/3.6 burndown.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/3.6 burndown.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="TV1y8TA3TYEfAarvJcViFXOBrUFIq+ml/5jzn6DSWts="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="4WxU4ya0dz0+BuIKDAbr/Zf2n51xOsnoyZfq2S1f3kg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Control del Sprint</t>
   </si>
@@ -38,13 +38,10 @@
     <t>Gestión de usuarios y roles</t>
   </si>
   <si>
-    <t>Iniciar sesión en la plataforma</t>
-  </si>
-  <si>
     <t>Registrar actividad de la etapa</t>
   </si>
   <si>
-    <t>Consulta detallada de las cajas quirúrgicas</t>
+    <t>Iniciar sesión en la plataforma</t>
   </si>
   <si>
     <t>Consulta de auditoría</t>
@@ -53,7 +50,7 @@
     <t>Control de acceso según rol</t>
   </si>
   <si>
-    <t>Registrar salida de insumos</t>
+    <t>Consulta detallada de las cajas quirúrgicas</t>
   </si>
   <si>
     <t>Configurar alertas de inventario</t>
@@ -62,19 +59,34 @@
     <t>Consulta de estado y ubicación de cajas quirúrgicas</t>
   </si>
   <si>
-    <t>Registrar reposición de insumos</t>
+    <t>Registrar salida de insumos</t>
+  </si>
+  <si>
+    <t>Funcionalidad agregar cajas quirúrgicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Historial de entregas de cajas quirúrgicas y materiales</t>
   </si>
   <si>
     <t>Registro de cambio de etapa de cajas quirúrgicas</t>
   </si>
   <si>
-    <t>Funcionalidad agregar cajas quirúrgicas</t>
+    <t>Registrar reposición de insumos</t>
+  </si>
+  <si>
+    <t>Consulta de estadísticas de producción de la Central</t>
   </si>
   <si>
     <t>Retroceder etapa</t>
   </si>
   <si>
-    <t>Historial de entregas de cajas quirúrgicas y materiales</t>
+    <t>Generación de reportes de producción de la Central</t>
+  </si>
+  <si>
+    <t>Reales de producto por realizar</t>
   </si>
   <si>
     <t>Consulta de inventarios por separado</t>
@@ -84,15 +96,6 @@
   </si>
   <si>
     <t>Consulta del catálogo digital de cajas quirúrgicas</t>
-  </si>
-  <si>
-    <t>Consulta de estadísticas de producción de la Central</t>
-  </si>
-  <si>
-    <t>Reales de producto por realizar</t>
-  </si>
-  <si>
-    <t>Generación de reportes de producción de la Central</t>
   </si>
   <si>
     <t>Estimadas de producto por realizar</t>
@@ -261,7 +264,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -279,6 +281,7 @@
       <left/>
       <right/>
       <top/>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -297,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="40">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -326,8 +329,17 @@
     <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="8" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -338,8 +350,17 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -350,8 +371,8 @@
     <xf borderId="15" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="14" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="11" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -359,8 +380,20 @@
     <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -443,7 +476,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint 1'!$B$14:$V$14</c:f>
+              <c:f>'Sprint 1'!$C$5:$V$5</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -472,17 +505,234 @@
           </c:cat>
           <c:val>
             <c:numRef>
+              <c:f>'Sprint 1'!$C$6:$V$6</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 1'!$B$7</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sprint 1'!$C$4:$V$4</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 1'!$C$7:$V$7</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 1'!$B$8</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sprint 1'!$C$4:$V$4</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 1'!$C$8:$V$8</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 1'!$B$9</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sprint 1'!$C$4:$V$4</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 1'!$C$9:$V$9</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 1'!$B$10</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sprint 1'!$C$4:$V$4</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 1'!$C$10:$V$10</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 1'!$B$11</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="8CB9E2"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sprint 1'!$C$4:$V$4</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 1'!$C$11:$V$11</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 1'!$A$14</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="F2A46F"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sprint 1'!$C$4:$V$4</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 1'!$B$14:$V$14</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 1'!$A$16</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="C0C0C0"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sprint 1'!$C$4:$V$4</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
               <c:f>'Sprint 1'!$B$16:$V$16</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="1822147549"/>
-        <c:axId val="2012110264"/>
+        <c:axId val="1387522149"/>
+        <c:axId val="460051546"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1822147549"/>
+        <c:axId val="1387522149"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -538,10 +788,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2012110264"/>
+        <c:crossAx val="460051546"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2012110264"/>
+        <c:axId val="460051546"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -607,7 +857,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1822147549"/>
+        <c:crossAx val="1387522149"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -690,7 +940,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint 2'!$B$10:$V$10</c:f>
+              <c:f>'Sprint 2'!$C$5:$V$5</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -719,17 +969,141 @@
           </c:cat>
           <c:val>
             <c:numRef>
+              <c:f>'Sprint 2'!$C$6:$V$6</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 2'!$B$7</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="A5A5A5"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sprint 2'!$C$4:$V$4</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 2'!$C$7:$V$7</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 2'!$B$8</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sprint 2'!$C$4:$V$4</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 2'!$C$8:$V$8</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 2'!$A$10</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sprint 2'!$C$4:$V$4</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 2'!$B$10:$V$10</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 2'!$A$12</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sprint 2'!$C$4:$V$4</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
               <c:f>'Sprint 2'!$B$12:$V$12</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="1768376615"/>
-        <c:axId val="1478856606"/>
+        <c:axId val="424723794"/>
+        <c:axId val="1185262222"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1768376615"/>
+        <c:axId val="424723794"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -785,10 +1159,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1478856606"/>
+        <c:crossAx val="1185262222"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1478856606"/>
+        <c:axId val="1185262222"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -854,7 +1228,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1768376615"/>
+        <c:crossAx val="424723794"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -972,11 +1346,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="1309035928"/>
-        <c:axId val="568127660"/>
+        <c:axId val="723938706"/>
+        <c:axId val="960978213"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1309035928"/>
+        <c:axId val="723938706"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1032,10 +1406,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568127660"/>
+        <c:crossAx val="960978213"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="568127660"/>
+        <c:axId val="960978213"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1101,7 +1475,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1309035928"/>
+        <c:crossAx val="723938706"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1139,7 +1513,7 @@
     <xdr:ext cx="3524250" cy="3257550"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="546580150" name="Chart 2" title="Gráfico"/>
+        <xdr:cNvPr id="546580150" name="Chart 3" title="Gráfico"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1169,7 +1543,7 @@
     <xdr:ext cx="3524250" cy="3257550"/>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1759702778" name="Chart 3" title="Gráfico"/>
+        <xdr:cNvPr id="1759702778" name="Chart 2" title="Gráfico"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1532,550 +1906,632 @@
     </row>
     <row r="5" ht="47.25" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
+        <v>7</v>
+      </c>
+      <c r="B5" s="12">
+        <v>17.0</v>
+      </c>
+      <c r="C5" s="14">
+        <v>4.0</v>
+      </c>
+      <c r="D5" s="15">
+        <v>4.0</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="15">
+        <v>3.0</v>
+      </c>
+      <c r="G5" s="15">
+        <v>6.0</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
       <c r="W5" s="3">
-        <f t="shared" ref="W5:W9" si="1">SUM(C5:V5)</f>
-        <v>0</v>
+        <f t="shared" ref="W5:W12" si="1">SUM(C5:V5)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="47.25" customHeight="1">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="19">
+        <v>14.0</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="I6" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="J6" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="K6" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="21">
+        <f t="shared" si="1"/>
         <v>10</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="16">
-        <f t="shared" si="1"/>
-        <v>0</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="16">
+      <c r="A7" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="26">
+        <v>18.0</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="22">
+        <v>6.0</v>
+      </c>
+      <c r="L7" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="M7" s="22">
+        <v>5.0</v>
+      </c>
+      <c r="N7" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="18"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="18"/>
+      <c r="W7" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" ht="47.25" customHeight="1">
-      <c r="A8" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="16">
+      <c r="A8" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="19">
+        <v>10.0</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="O8" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="P8" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="18"/>
+      <c r="W8" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" ht="47.25" customHeight="1">
-      <c r="A9" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="16">
+      <c r="A9" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="33">
+        <v>9.0</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="O9" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="P9" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="Q9" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" ht="47.25" customHeight="1">
-      <c r="A10" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="16"/>
+      <c r="A10" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="19">
+        <v>7.0</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="R10" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="S10" s="18"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
+      <c r="V10" s="18"/>
+      <c r="W10" s="21">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="11" ht="47.25" customHeight="1">
-      <c r="A11" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="16"/>
+      <c r="A11" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="33">
+        <v>10.0</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="P11" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="Q11" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="R11" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="S11" s="18"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="21">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="12" ht="47.25" customHeight="1">
-      <c r="A12" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="23"/>
-      <c r="S12" s="23"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="24">
-        <f>SUM(C12:V12)</f>
-        <v>0</v>
+      <c r="A12" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="19">
+        <v>11.0</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="R12" s="30">
+        <v>4.0</v>
+      </c>
+      <c r="S12" s="30">
+        <v>4.0</v>
+      </c>
+      <c r="T12" s="30">
+        <v>3.0</v>
+      </c>
+      <c r="U12" s="31"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="34">
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="23.25" customHeight="1"/>
     <row r="14" ht="34.5" customHeight="1">
-      <c r="A14" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="26">
+      <c r="A14" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="36">
         <f>SUM(B5:B13)</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="26">
+        <v>96</v>
+      </c>
+      <c r="C14" s="36">
         <f t="shared" ref="C14:V14" si="2">B14-SUM(C5:C12)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="26">
+        <v>92</v>
+      </c>
+      <c r="D14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="26">
+        <v>88</v>
+      </c>
+      <c r="E14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F14" s="26">
+        <v>88</v>
+      </c>
+      <c r="F14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="26">
+        <v>85</v>
+      </c>
+      <c r="G14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="26">
+        <v>79</v>
+      </c>
+      <c r="H14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="26">
+        <v>76</v>
+      </c>
+      <c r="I14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J14" s="26">
+        <v>75</v>
+      </c>
+      <c r="J14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K14" s="26">
+        <v>71</v>
+      </c>
+      <c r="K14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L14" s="26">
+        <v>63</v>
+      </c>
+      <c r="L14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="26">
+        <v>59</v>
+      </c>
+      <c r="M14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="26">
+        <v>54</v>
+      </c>
+      <c r="N14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="26">
+        <v>47</v>
+      </c>
+      <c r="O14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="26">
+        <v>36</v>
+      </c>
+      <c r="P14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="26">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="26">
+        <v>21</v>
+      </c>
+      <c r="R14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="26">
+        <v>14</v>
+      </c>
+      <c r="S14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="26">
+        <v>10</v>
+      </c>
+      <c r="T14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="26">
+        <v>7</v>
+      </c>
+      <c r="U14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V14" s="26">
+        <v>7</v>
+      </c>
+      <c r="V14" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" ht="23.25" customHeight="1">
-      <c r="A15" s="27"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="26"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
-      <c r="U15" s="26"/>
-      <c r="V15" s="26"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
+      <c r="S15" s="36"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="36"/>
+      <c r="V15" s="36"/>
     </row>
     <row r="16" ht="36.0" customHeight="1">
-      <c r="A16" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="26">
+      <c r="A16" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="36">
         <f>SUM(B5:B12)</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="26">
+        <v>96</v>
+      </c>
+      <c r="C16" s="36">
         <f t="shared" ref="C16:V16" si="3">B16-(SUM($B$5:$B$12)/20)</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="26">
+        <v>91.2</v>
+      </c>
+      <c r="D16" s="36">
+        <f t="shared" si="3"/>
+        <v>86.4</v>
+      </c>
+      <c r="E16" s="36">
+        <f t="shared" si="3"/>
+        <v>81.6</v>
+      </c>
+      <c r="F16" s="36">
+        <f t="shared" si="3"/>
+        <v>76.8</v>
+      </c>
+      <c r="G16" s="36">
+        <f t="shared" si="3"/>
+        <v>72</v>
+      </c>
+      <c r="H16" s="36">
+        <f t="shared" si="3"/>
+        <v>67.2</v>
+      </c>
+      <c r="I16" s="36">
+        <f t="shared" si="3"/>
+        <v>62.4</v>
+      </c>
+      <c r="J16" s="36">
+        <f t="shared" si="3"/>
+        <v>57.6</v>
+      </c>
+      <c r="K16" s="36">
+        <f t="shared" si="3"/>
+        <v>52.8</v>
+      </c>
+      <c r="L16" s="36">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="M16" s="36">
+        <f t="shared" si="3"/>
+        <v>43.2</v>
+      </c>
+      <c r="N16" s="36">
+        <f t="shared" si="3"/>
+        <v>38.4</v>
+      </c>
+      <c r="O16" s="36">
+        <f t="shared" si="3"/>
+        <v>33.6</v>
+      </c>
+      <c r="P16" s="36">
+        <f t="shared" si="3"/>
+        <v>28.8</v>
+      </c>
+      <c r="Q16" s="36">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="R16" s="36">
+        <f t="shared" si="3"/>
+        <v>19.2</v>
+      </c>
+      <c r="S16" s="36">
+        <f t="shared" si="3"/>
+        <v>14.4</v>
+      </c>
+      <c r="T16" s="36">
+        <f t="shared" si="3"/>
+        <v>9.6</v>
+      </c>
+      <c r="U16" s="36">
+        <f t="shared" si="3"/>
+        <v>4.8</v>
+      </c>
+      <c r="V16" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
     </row>
     <row r="19">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
     </row>
     <row r="20">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22">
-      <c r="A22" s="28"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="28"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="28"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="28"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="28"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
@@ -3187,436 +3643,464 @@
     </row>
     <row r="5" ht="47.25" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="B5" s="12">
+        <v>17.0</v>
+      </c>
+      <c r="C5" s="14">
+        <v>3.0</v>
+      </c>
+      <c r="D5" s="15">
+        <v>2.0</v>
+      </c>
+      <c r="E5" s="15">
+        <v>5.0</v>
+      </c>
+      <c r="F5" s="15">
+        <v>5.0</v>
+      </c>
+      <c r="G5" s="15">
+        <v>2.0</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
       <c r="W5" s="3">
         <f t="shared" ref="W5:W8" si="1">SUM(C5:V5)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="47.25" customHeight="1">
-      <c r="A6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="16">
+      <c r="A6" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="19">
+        <v>14.0</v>
+      </c>
+      <c r="C6" s="20">
+        <v>3.0</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="16">
+      <c r="A7" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="26">
+        <v>17.0</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="18"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="18"/>
+      <c r="W7" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="47.25" customHeight="1">
-      <c r="A8" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="24">
+      <c r="A8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="19">
+        <v>17.0</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="31"/>
+      <c r="W8" s="34">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="23.25" customHeight="1"/>
     <row r="10" ht="34.5" customHeight="1">
-      <c r="A10" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="26">
+      <c r="A10" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="36">
         <f>SUM(B5:B9)</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="26">
+        <v>65</v>
+      </c>
+      <c r="C10" s="36">
         <f t="shared" ref="C10:V10" si="2">B10-SUM(C5:C8)</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="26">
+        <v>59</v>
+      </c>
+      <c r="D10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E10" s="26">
+        <v>53</v>
+      </c>
+      <c r="E10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="26">
+        <v>48</v>
+      </c>
+      <c r="F10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="26">
+        <v>43</v>
+      </c>
+      <c r="G10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="26">
+        <v>41</v>
+      </c>
+      <c r="H10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="26">
+        <v>41</v>
+      </c>
+      <c r="I10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="26">
+        <v>41</v>
+      </c>
+      <c r="J10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="26">
+        <v>41</v>
+      </c>
+      <c r="K10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="26">
+        <v>41</v>
+      </c>
+      <c r="L10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="26">
+        <v>41</v>
+      </c>
+      <c r="M10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N10" s="26">
+        <v>41</v>
+      </c>
+      <c r="N10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="26">
+        <v>41</v>
+      </c>
+      <c r="O10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P10" s="26">
+        <v>41</v>
+      </c>
+      <c r="P10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="26">
+        <v>41</v>
+      </c>
+      <c r="Q10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R10" s="26">
+        <v>41</v>
+      </c>
+      <c r="R10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S10" s="26">
+        <v>41</v>
+      </c>
+      <c r="S10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T10" s="26">
+        <v>41</v>
+      </c>
+      <c r="T10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="26">
+        <v>41</v>
+      </c>
+      <c r="U10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V10" s="26">
+        <v>41</v>
+      </c>
+      <c r="V10" s="36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" ht="23.25" customHeight="1">
-      <c r="A11" s="27"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="26"/>
-      <c r="S11" s="26"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="26"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
+      <c r="S11" s="36"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="36"/>
     </row>
     <row r="12" ht="36.0" customHeight="1">
-      <c r="A12" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="26">
+      <c r="A12" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="36">
         <f>SUM(B5:B8)</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="26">
+        <v>65</v>
+      </c>
+      <c r="C12" s="36">
         <f t="shared" ref="C12:V12" si="3">B12-(SUM($B$5:$B$8)/20)</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="26">
+        <v>61.75</v>
+      </c>
+      <c r="D12" s="36">
+        <f t="shared" si="3"/>
+        <v>58.5</v>
+      </c>
+      <c r="E12" s="36">
+        <f t="shared" si="3"/>
+        <v>55.25</v>
+      </c>
+      <c r="F12" s="36">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="G12" s="36">
+        <f t="shared" si="3"/>
+        <v>48.75</v>
+      </c>
+      <c r="H12" s="36">
+        <f t="shared" si="3"/>
+        <v>45.5</v>
+      </c>
+      <c r="I12" s="36">
+        <f t="shared" si="3"/>
+        <v>42.25</v>
+      </c>
+      <c r="J12" s="36">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="K12" s="36">
+        <f t="shared" si="3"/>
+        <v>35.75</v>
+      </c>
+      <c r="L12" s="36">
+        <f t="shared" si="3"/>
+        <v>32.5</v>
+      </c>
+      <c r="M12" s="36">
+        <f t="shared" si="3"/>
+        <v>29.25</v>
+      </c>
+      <c r="N12" s="36">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="O12" s="36">
+        <f t="shared" si="3"/>
+        <v>22.75</v>
+      </c>
+      <c r="P12" s="36">
+        <f t="shared" si="3"/>
+        <v>19.5</v>
+      </c>
+      <c r="Q12" s="36">
+        <f t="shared" si="3"/>
+        <v>16.25</v>
+      </c>
+      <c r="R12" s="36">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="S12" s="36">
+        <f t="shared" si="3"/>
+        <v>9.75</v>
+      </c>
+      <c r="T12" s="36">
+        <f t="shared" si="3"/>
+        <v>6.5</v>
+      </c>
+      <c r="U12" s="36">
+        <f t="shared" si="3"/>
+        <v>3.25</v>
+      </c>
+      <c r="V12" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V12" s="26">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
     </row>
     <row r="15">
-      <c r="A15" s="28"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
     </row>
     <row r="16">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
     </row>
     <row r="17">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
     </row>
     <row r="18">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="28"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1"/>
@@ -4732,513 +5216,513 @@
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
       <c r="W5" s="3">
         <f t="shared" ref="W5:W7" si="1">SUM(C5:V5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="47.25" customHeight="1">
-      <c r="A6" s="13" t="s">
-        <v>9</v>
+      <c r="A6" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="16">
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1">
-      <c r="A7" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="16">
+      <c r="A7" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="24"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="18"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="18"/>
+      <c r="W7" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="47.25" customHeight="1">
-      <c r="A8" s="13" t="s">
-        <v>16</v>
+      <c r="A8" s="16" t="s">
+        <v>14</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="16"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="18"/>
+      <c r="W8" s="21"/>
     </row>
     <row r="9" ht="47.25" customHeight="1">
-      <c r="A9" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="16"/>
+      <c r="A9" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="21"/>
     </row>
     <row r="10" ht="47.25" customHeight="1">
-      <c r="A10" s="13" t="s">
-        <v>22</v>
+      <c r="A10" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
+      <c r="V10" s="18"/>
+      <c r="W10" s="21"/>
     </row>
     <row r="11" ht="47.25" customHeight="1">
-      <c r="A11" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
-      <c r="R11" s="23"/>
-      <c r="S11" s="23"/>
-      <c r="T11" s="23"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="24">
+      <c r="A11" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="34">
         <f>SUM(C11:V11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="23.25" customHeight="1"/>
     <row r="13" ht="34.5" customHeight="1">
-      <c r="A13" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="26">
+      <c r="A13" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="36">
         <f t="shared" ref="C13:V13" si="2">B13-SUM(C5:C11)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L13" s="26">
+      <c r="L13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O13" s="26">
+      <c r="O13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P13" s="26">
+      <c r="P13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="26">
+      <c r="Q13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R13" s="26">
+      <c r="R13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S13" s="26">
+      <c r="S13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T13" s="26">
+      <c r="T13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U13" s="26">
+      <c r="U13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V13" s="26">
+      <c r="V13" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="23.25" customHeight="1">
-      <c r="A14" s="27"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="26"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="26"/>
-      <c r="T14" s="26"/>
-      <c r="U14" s="26"/>
-      <c r="V14" s="26"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
+      <c r="S14" s="36"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="36"/>
     </row>
     <row r="15" ht="36.0" customHeight="1">
-      <c r="A15" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="26">
+      <c r="A15" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="36">
         <f>SUM(B5:B11)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="36">
         <f t="shared" ref="C15:V15" si="3">B15-(SUM($B$5:$B$11)/20)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L15" s="26">
+      <c r="L15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O15" s="26">
+      <c r="O15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P15" s="26">
+      <c r="P15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="26">
+      <c r="Q15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S15" s="26">
+      <c r="S15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T15" s="26">
+      <c r="T15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U15" s="26">
+      <c r="U15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V15" s="26">
+      <c r="V15" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
     </row>
     <row r="18">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
     </row>
     <row r="19">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
     </row>
     <row r="20">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="28"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="28"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="28"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="28"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>
